--- a/test.xlsx
+++ b/test.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DA5E44-D18C-46F4-AFA6-D5EB86A3F42A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF766DA-5C74-44B7-A3C3-8032D349B8CE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,247 +332,157 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
-      <c r="B11">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
-      <c r="B12">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
-      <c r="B13">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
-      <c r="B14">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
-      <c r="B15">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
-      <c r="B16">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
-      <c r="B17">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
-      <c r="B18">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
-      <c r="B19">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
-      <c r="B20">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
-      <c r="B21">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
-      <c r="B22">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
-      <c r="B23">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
-      <c r="B24">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
-      <c r="B25">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26</v>
       </c>
-      <c r="B26">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>27</v>
       </c>
-      <c r="B27">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>28</v>
       </c>
-      <c r="B28">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>29</v>
       </c>
-      <c r="B29">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>30</v>
-      </c>
-      <c r="B30">
-        <v>390</v>
       </c>
     </row>
   </sheetData>
